--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/WYOMING_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/WYOMING_2015.xlsx
@@ -409,7 +409,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="10">
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="11">
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="13">
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="16">
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="17">
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="18">
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="19">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="24">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="26">
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="29">
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="D36">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="37">
@@ -1111,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="D42">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="43">
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="D44">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="45">
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="49">
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="50">
@@ -1255,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="D50">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="51">
@@ -1273,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="D51">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="52">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="54">
@@ -1543,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="67">
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="69">
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="D70">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="71">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C71">
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="73">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="74">
@@ -1687,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="D74">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="75">
@@ -1723,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="D76">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="77">
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="79">
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="D79">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="80">
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="D80">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="81">
@@ -1849,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="84">
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="D85">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="86">
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="87">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="88">
@@ -1939,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="89">
@@ -1957,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="90">
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="91">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="92">
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="94">
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="98">
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="100">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C104">
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="106">
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="110">
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="112">
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="D112">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="113">
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="118">
@@ -2479,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="119">
@@ -2497,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="D119">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="120">
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="D120">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="121">
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="122">
@@ -2551,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="D122">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="123">
@@ -2569,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="D123">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="124">
@@ -2623,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="D126">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="127">
@@ -2641,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="D127">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="128">
@@ -2659,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="D128">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="129">
@@ -2677,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="D129">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="130">
@@ -2695,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="D130">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="131">
@@ -2713,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="132">
@@ -2731,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="133">
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="D133">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="134">
@@ -2767,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="D134">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="135">
@@ -2785,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="D135">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="136">
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="D136">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="137">
@@ -2821,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="D137">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="138">
@@ -2839,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="D138">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="139">
@@ -2857,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="D139">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="140">
@@ -2893,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="D141">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="142">
@@ -2929,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="D143">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="144">
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="D145">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="146">
@@ -2983,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="D146">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="147">
@@ -3055,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="D150">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="151">
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="D151">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="152">
@@ -3091,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="D152">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="153">
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="D154">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="155">
@@ -3145,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="D155">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="156">
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="D156">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="157">
@@ -3181,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="D157">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="158">
@@ -3199,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="D158">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="159">
@@ -3217,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="D159">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="160">
@@ -3253,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="D161">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="162">
@@ -3289,7 +3289,7 @@
         <v>1</v>
       </c>
       <c r="D163">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="164">
@@ -3307,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="D164">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="165">
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="D167">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="168">
@@ -3379,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="D168">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="169">
@@ -3415,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="D170">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="171">
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="D172">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="173">
@@ -3487,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="D174">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="175">
@@ -3523,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="D176">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="177">
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="D177">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="178">
@@ -3559,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="D178">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="179">
@@ -3577,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="D179">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="180">
@@ -3595,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="D180">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="181">
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="D181">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="182">
@@ -3649,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="D183">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="184">
@@ -3685,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="D185">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="186">
@@ -3703,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="D186">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="187">
@@ -3793,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="D191">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="192">
@@ -3811,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="193">
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="D196">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="197">
@@ -3919,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="D198">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="199">
@@ -3937,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="D199">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="200">
@@ -3955,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="D200">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="201">
@@ -3973,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="D201">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="202">
@@ -4027,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="D204">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="205">
@@ -4045,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="D205">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="206">
@@ -4063,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="D206">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="207">
@@ -4099,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="209">
@@ -4171,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="D212">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="213">
@@ -4189,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="D213">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="214">
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="D214">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="215">
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="D216">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="217">
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="D217">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="218">
@@ -4279,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="D218">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="219">
@@ -4297,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="D219">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="220">
@@ -4315,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="D220">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="221">
@@ -4333,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="D221">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="222">
@@ -4369,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="D223">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="224">
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="D224">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="225">
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="D225">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="226">
@@ -4441,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="D227">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="228">
@@ -4459,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="D228">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="229">
@@ -4477,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="D229">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="230">
@@ -4495,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="D230">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="231">
@@ -4513,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="D231">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="232">
@@ -4531,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="D232">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="233">
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="D235">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="236">
@@ -4603,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="D236">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="237">
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="D237">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="238">
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="D239">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="240">
@@ -4675,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="241">
@@ -4747,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="D244">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="245">
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="D246">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="247">
@@ -4801,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="D247">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="248">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="D249">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="250">
@@ -4855,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="251">
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="D251">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="252">
@@ -4891,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="D252">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="253">
@@ -4963,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="D256">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="257">
@@ -4999,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="D258">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="259">
@@ -5017,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="D259">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="260">
@@ -5035,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="D260">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="261">
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="D261">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="262">
@@ -5089,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="D263">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="264">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="D264">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="265">
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="D265">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="266">
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="D267">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="268">
@@ -5179,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="D268">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="269">
@@ -5215,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="D270">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="271">
@@ -5233,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="D271">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="272">
@@ -5269,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="D273">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="274">
@@ -5305,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="D275">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="276">
@@ -5341,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="D277">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="278">
@@ -5395,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="D280">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="281">
@@ -5413,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="D281">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="282">
@@ -5449,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="D283">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="284">
@@ -5467,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="D284">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="285">
@@ -5485,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="D285">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="286">
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="D286">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="287">
@@ -5557,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="D289">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="290">
@@ -5575,7 +5575,7 @@
         <v>1</v>
       </c>
       <c r="D290">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="291">
@@ -5611,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="D292">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="293">
@@ -5629,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="D293">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="294">
@@ -5647,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="D294">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="295">
@@ -5665,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="D295">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="296">
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="D297">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="298">
@@ -5863,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="D306">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="307">
@@ -5989,7 +5989,7 @@
         <v>1</v>
       </c>
       <c r="D313">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="314">
@@ -6007,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="D314">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="315">
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="317">
@@ -6061,7 +6061,7 @@
         <v>1</v>
       </c>
       <c r="D317">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="318">
@@ -6079,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="D318">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="319">
@@ -6115,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="D320">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="321">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="D321">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="322">
@@ -6169,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="D323">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="324">
@@ -6187,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="D324">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="325">
@@ -6223,7 +6223,7 @@
         <v>1</v>
       </c>
       <c r="D326">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="327">
@@ -6241,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="D327">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="328">
@@ -6313,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="D331">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="332">
@@ -6331,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="D332">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="333">
@@ -6349,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="D333">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="334">
@@ -6367,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="D334">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="335">
@@ -6385,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="D335">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="336">
@@ -6403,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="D336">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="337">
@@ -6439,7 +6439,7 @@
         <v>1</v>
       </c>
       <c r="D338">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="339">
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="D341">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="342">
@@ -6511,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="D342">
-        <v>0.0009082652134423251</v>
+        <v>0.0009082652134423252</v>
       </c>
     </row>
     <row r="343">
